--- a/processed_data/hard_data_exports/hunt_tables/2026/CLEAN_XLXS_STAGED/2026 ELK BULL L.E - PRIVATE LAND ONLY MUZZLELOADER.xlsx
+++ b/processed_data/hard_data_exports/hunt_tables/2026/CLEAN_XLXS_STAGED/2026 ELK BULL L.E - PRIVATE LAND ONLY MUZZLELOADER.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O22"/>
+  <dimension ref="A1:P22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -577,10 +577,15 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Average Age Harvested (previous hunting season)</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
+          <t>Average Harvest Age</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Current Age (3-Yr Avg)</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Avg Days Hunted (previous hunting season)</t>
         </is>
@@ -637,7 +642,8 @@
           <t>9.1</t>
         </is>
       </c>
-      <c r="O2" s="2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" s="2" t="inlineStr"/>
     </row>
     <row r="3" ht="42" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
@@ -690,7 +696,8 @@
           <t>8.3</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" s="3" t="inlineStr"/>
     </row>
     <row r="4" ht="42" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
@@ -743,7 +750,8 @@
           <t>7</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" s="2" t="inlineStr"/>
     </row>
     <row r="5" ht="42" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -796,7 +804,8 @@
           <t>7.1</t>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" s="3" t="inlineStr"/>
     </row>
     <row r="6" ht="42" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
@@ -857,7 +866,8 @@
           <t>6.5</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>4.5</t>
         </is>
@@ -914,7 +924,8 @@
           <t>7.7</t>
         </is>
       </c>
-      <c r="O7" s="3" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" s="3" t="inlineStr"/>
     </row>
     <row r="8" ht="42" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
@@ -967,7 +978,8 @@
           <t>5.7</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" s="2" t="inlineStr"/>
     </row>
     <row r="9" ht="42" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
@@ -1020,7 +1032,8 @@
           <t>9.1</t>
         </is>
       </c>
-      <c r="O9" s="3" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" s="3" t="inlineStr"/>
     </row>
     <row r="10" ht="42" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
@@ -1073,7 +1086,8 @@
           <t>7.8</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" s="2" t="inlineStr"/>
     </row>
     <row r="11" ht="42" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
@@ -1126,7 +1140,8 @@
           <t>5.7</t>
         </is>
       </c>
-      <c r="O11" s="3" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" s="3" t="inlineStr"/>
     </row>
     <row r="12" ht="42" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
@@ -1179,7 +1194,8 @@
           <t>7.8</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" s="2" t="inlineStr"/>
     </row>
     <row r="13" ht="42" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
@@ -1232,7 +1248,8 @@
           <t>6.9</t>
         </is>
       </c>
-      <c r="O13" s="3" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" s="3" t="inlineStr"/>
     </row>
     <row r="14" ht="42" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
@@ -1285,7 +1302,8 @@
           <t>7.6</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" s="2" t="inlineStr"/>
     </row>
     <row r="15" ht="42" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
@@ -1338,7 +1356,8 @@
           <t>7</t>
         </is>
       </c>
-      <c r="O15" s="3" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" s="3" t="inlineStr"/>
     </row>
     <row r="16" ht="42" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
@@ -1391,7 +1410,8 @@
           <t>5</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
@@ -1448,7 +1468,8 @@
           <t>6.4</t>
         </is>
       </c>
-      <c r="O17" s="3" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" s="3" t="inlineStr"/>
     </row>
     <row r="18" ht="42" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
@@ -1501,7 +1522,8 @@
           <t>7.8</t>
         </is>
       </c>
-      <c r="O18" s="2" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" s="2" t="inlineStr"/>
     </row>
     <row r="19" ht="42" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
@@ -1554,7 +1576,8 @@
           <t>6.6</t>
         </is>
       </c>
-      <c r="O19" s="3" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" s="3" t="inlineStr"/>
     </row>
     <row r="20" ht="42" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
@@ -1602,8 +1625,13 @@
       </c>
       <c r="L20" s="2" t="inlineStr"/>
       <c r="M20" s="2" t="inlineStr"/>
-      <c r="N20" s="2" t="inlineStr"/>
-      <c r="O20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" s="2" t="inlineStr"/>
     </row>
     <row r="21" ht="42" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
@@ -1651,8 +1679,13 @@
       </c>
       <c r="L21" s="3" t="inlineStr"/>
       <c r="M21" s="3" t="inlineStr"/>
-      <c r="N21" s="3" t="inlineStr"/>
-      <c r="O21" s="3" t="inlineStr"/>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" s="3" t="inlineStr"/>
     </row>
     <row r="22" ht="42" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
@@ -1708,8 +1741,13 @@
           <t>100</t>
         </is>
       </c>
-      <c r="N22" s="2" t="inlineStr"/>
-      <c r="O22" s="2" t="inlineStr">
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" s="2" t="inlineStr">
         <is>
           <t>3.2</t>
         </is>
